--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95E27F6-7CF7-4056-90D0-DF07DCB63BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A578EC6-A62A-41CE-96FD-D335899DEE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -497,14 +497,6 @@
       </rPr>
       <t>帮忙。</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/016/016_01.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/016/016_02.png</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -604,6 +596,98 @@
   </si>
   <si>
     <t>014_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_01.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02.png</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1175,7 +1259,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1569,7 +1653,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>48</v>
@@ -1591,7 +1675,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>51</v>
@@ -1670,7 +1754,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1690,7 +1774,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1710,7 +1794,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1730,7 +1814,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1750,7 +1834,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A578EC6-A62A-41CE-96FD-D335899DEE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0E5210-0D43-440F-8B31-2C8E88EDA53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -364,10 +364,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>先生是犬子的救命恩人，有什么本王能帮上忙的一定尽力而为。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>李</t>
     </r>
@@ -518,8 +514,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>草民</t>
+    <t>014_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/01</t>
     </r>
     <r>
       <rPr>
@@ -529,7 +529,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>自幼读四书五经，诸子百家，文章未成，宦术未精，所学唯有为生民立命而已，</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -539,7 +539,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>若以我一命</t>
+      <t>/01</t>
     </r>
     <r>
       <rPr>
@@ -549,7 +549,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>换千万民生，吾往矣</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -559,12 +559,84 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>_01.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>先生是犬子的救命恩人，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若有本王能帮上忙的，一定尽力而为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>先生所言让本王惭愧啊…我会修书一封密奏皇上赈灾药材之事，先生也切莫再和别人提及此事，万事小心。</t>
+    <t>先生所言让本王惭愧啊…待我会写一道密奏，向皇上禀明赈灾药材之事。先生也切莫再和别人提及此事。</t>
     <rPh sb="0" eb="2">
       <t>センセイ</t>
     </rPh>
@@ -586,21 +658,17 @@
     <rPh sb="9" eb="10">
       <t>ア</t>
     </rPh>
-    <rPh sb="11" eb="12">
+    <rPh sb="12" eb="13">
       <t>ガ</t>
     </rPh>
-    <rPh sb="12" eb="13">
+    <rPh sb="13" eb="14">
       <t>カイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>014_02</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/01</t>
+    <r>
+      <t>草民</t>
     </r>
     <r>
       <rPr>
@@ -610,7 +678,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>5</t>
+      <t>自幼读四书五经，诸子百家，文章未成，功名未就，所学所求只有为生民立命，</t>
     </r>
     <r>
       <rPr>
@@ -620,7 +688,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>/01</t>
+      <t>若以我一命</t>
     </r>
     <r>
       <rPr>
@@ -630,7 +698,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>5</t>
+      <t>换千万民生，吾往矣</t>
     </r>
     <r>
       <rPr>
@@ -640,53 +708,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>_01.png</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>/01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02.png</t>
+      <t>。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -1259,7 +1281,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1653,7 +1675,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>48</v>
@@ -1675,7 +1697,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>51</v>
@@ -1698,7 +1720,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1718,7 +1740,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1734,7 +1756,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1754,7 +1776,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1774,7 +1796,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1794,7 +1816,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1814,7 +1836,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1834,7 +1856,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0E5210-0D43-440F-8B31-2C8E88EDA53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F18600-89E1-49F3-9D75-A1786BCD4C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="62">
   <si>
     <t>StoryID</t>
   </si>
@@ -68,10 +68,6 @@
   </si>
   <si>
     <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>right</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1215,73 +1211,73 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="K1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1396,10 +1392,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
@@ -1417,10 +1413,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1431,16 +1427,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1451,7 +1447,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>9</v>
@@ -1460,7 +1456,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1471,16 +1467,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1491,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>9</v>
@@ -1500,7 +1496,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1511,16 +1507,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1531,7 +1527,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>9</v>
@@ -1540,7 +1536,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1551,16 +1547,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1571,7 +1567,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>9</v>
@@ -1580,7 +1576,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1591,16 +1587,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1611,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>9</v>
@@ -1620,7 +1616,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1631,16 +1627,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1651,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>9</v>
@@ -1660,7 +1656,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1675,10 +1671,10 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1689,18 +1685,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1711,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>9</v>
@@ -1720,7 +1716,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1731,16 +1727,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1756,7 +1752,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1767,16 +1763,16 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1787,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>9</v>
@@ -1796,7 +1792,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1807,16 +1803,16 @@
         <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1827,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>9</v>
@@ -1836,7 +1832,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1847,16 +1843,16 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F18600-89E1-49F3-9D75-A1786BCD4C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A545C-DE92-42CE-AA56-E49FD68066B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -632,7 +632,53 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>先生所言让本王惭愧啊…待我会写一道密奏，向皇上禀明赈灾药材之事。先生也切莫再和别人提及此事。</t>
+    <r>
+      <t>草民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自幼读四书五经，诸子百家，文章未成，功名未就，所学所求只有为生民立命，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>若以我一命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>换千万民生，吾往矣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>先生所言让本王惭愧啊…待本王修一道密疏，向圣上禀明此事。先生也切莫再向他人提及。</t>
     <rPh sb="0" eb="2">
       <t>センセイ</t>
     </rPh>
@@ -654,58 +700,6 @@
     <rPh sb="9" eb="10">
       <t>ア</t>
     </rPh>
-    <rPh sb="12" eb="13">
-      <t>ガ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>カイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>草民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自幼读四书五经，诸子百家，文章未成，功名未就，所学所求只有为生民立命，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>若以我一命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>换千万民生，吾往矣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1832,7 +1826,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1852,7 +1846,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5A545C-DE92-42CE-AA56-E49FD68066B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F34B79-19E7-4DD7-A63A-9F14D509C114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="62">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
   <si>
     <t>LineIndex</t>
   </si>
@@ -79,64 +65,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>night</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>current_scene</t>
@@ -702,16 +637,101 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -725,7 +745,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -746,20 +766,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -780,8 +792,30 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -796,20 +830,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -840,7 +876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -863,24 +899,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -890,7 +915,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -899,9 +924,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1179,176 +1235,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="24" customFormat="1">
+      <c r="A1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="S1" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="24" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="26">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="25"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="L3" s="17"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="13"/>
+      <c r="T2" s="27"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="12"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="13"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="13"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="13"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="13"/>
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{F85EB7FB-4170-4AC2-9DCB-2798AC2EBF97}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{E47B0860-F450-4CFE-B452-D4318F74AF92}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{DF70FF0E-85F9-4754-B37C-ED93E81C9B9A}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{1ACF20A9-1025-4504-994B-A1FB66EBF599}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{9730D905-4D4B-4BF3-9C6B-6688F9FC5F0B}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1358,41 +1441,41 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1400,17 +1483,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>32</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1418,19 +1501,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="18" t="s">
-        <v>35</v>
+      <c r="H3" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1438,19 +1521,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="19" t="s">
-        <v>36</v>
+      <c r="H4" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1458,19 +1541,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="18" t="s">
-        <v>37</v>
+      <c r="H5" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1478,19 +1561,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1498,19 +1581,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="20" t="s">
-        <v>39</v>
+      <c r="H7" s="15" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1518,19 +1601,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1538,19 +1621,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1558,19 +1641,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1578,19 +1661,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1598,19 +1681,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="21" t="s">
-        <v>44</v>
+      <c r="H12" s="16" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1618,19 +1701,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1638,19 +1721,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1658,17 +1741,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1676,21 +1759,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1698,19 +1781,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1718,19 +1801,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1738,15 +1821,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="18"/>
+        <v>5</v>
+      </c>
+      <c r="C19" s="13"/>
       <c r="D19" s="7"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1754,19 +1837,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="20" t="s">
-        <v>53</v>
+      <c r="H20" s="15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1774,19 +1857,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="20" t="s">
-        <v>54</v>
+      <c r="H21" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1794,19 +1877,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="20" t="s">
-        <v>55</v>
+      <c r="H22" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1814,19 +1897,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1834,19 +1917,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="20" t="s">
-        <v>61</v>
+      <c r="H24" s="15" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/DataTables/DetailText/剧情/015雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/015雷万钧归来.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F34B79-19E7-4DD7-A63A-9F14D509C114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CDD1AD-6DDE-4410-A82C-D3EC31754473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
   <si>
     <t>LineIndex</t>
   </si>
@@ -722,6 +733,10 @@
     <t>奖励心得</t>
     <phoneticPr fontId="10"/>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -731,7 +746,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -745,7 +760,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -766,7 +781,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -876,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -955,9 +970,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1236,25 +1254,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="24" customFormat="1">
+    <row r="1" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A1" s="17" t="s">
         <v>47</v>
       </c>
@@ -1316,7 +1334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="24" customFormat="1">
+    <row r="2" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
@@ -1438,21 +1456,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1477,8 +1495,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1495,8 +1516,9 @@
       <c r="H2" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1515,8 +1537,9 @@
       <c r="H3" s="13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1535,8 +1558,9 @@
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1555,8 +1579,9 @@
       <c r="H5" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1575,8 +1600,9 @@
       <c r="H6" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1595,8 +1621,9 @@
       <c r="H7" s="15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1615,8 +1642,9 @@
       <c r="H8" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1635,8 +1663,9 @@
       <c r="H9" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1655,8 +1684,9 @@
       <c r="H10" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1675,8 +1705,9 @@
       <c r="H11" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1695,8 +1726,9 @@
       <c r="H12" s="16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1735,8 +1768,9 @@
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1753,8 +1787,9 @@
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1775,8 +1810,9 @@
       <c r="H16" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1795,8 +1831,9 @@
       <c r="H17" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1815,8 +1852,9 @@
       <c r="H18" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1831,8 +1869,9 @@
       <c r="H19" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1851,8 +1890,9 @@
       <c r="H20" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1871,8 +1911,9 @@
       <c r="H21" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1891,8 +1932,9 @@
       <c r="H22" s="15" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1911,8 +1953,9 @@
       <c r="H23" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1931,8 +1974,9 @@
       <c r="H24" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1941,8 +1985,9 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1951,6 +1996,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
